--- a/output/北塩原村_業務進捗管理表.xlsx
+++ b/output/北塩原村_業務進捗管理表.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_変更管理・打合せ記録" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$M$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>基準日：令和8年8月18日</t>
+          <t>基準日：令和8年8月27日</t>
         </is>
       </c>
     </row>
@@ -804,303 +804,286 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>同月、国が「障害福祉計画策定に係る実態調査及びPDCAサイクルに関するマニュアル」を改定し、福島県から市町村へ通知された（8生福第2646号・8こ第2041号）。全81頁を読み、成果物と突合した。別表第五を適用しないという当方の判定は国の文書で裏付けられた一方、調査票に国の標準項目3件（外出の目的・介護保険の利用状況・強度行動障害の該当有無）が欠けていることが確認された。いずれも発送前でなければ対応できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>■ 警戒事項</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>アンケートの発送が工程案の令和8年8月上旬に間に合わない</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>回収期間または集計期間が圧縮され、報告書・計画書の工程に波及する</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>印刷仕様を確定し、宛名ラベルの提供日を村と合意する。遅延が確定した場合は回収期間を維持して集計以降を短縮する</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>村の実績データが29件中21件未受領</t>
+          <t>アンケートの発送が工程案の令和8年8月上旬に間に合わない</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>現行計画の評価、成果目標の現状値、見込量、給付費のいずれも確定できない</t>
+          <t>回収期間または集計期間が圧縮され、報告書・計画書の工程に波及する</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>最優先6件について9月末までの回答を求める。とくに年齢別・サービス別の匿名利用者一覧が個別積上げの前提となる</t>
+          <t>印刷仕様を確定し、宛名ラベルの提供日を村と合意する。遅延が確定した場合は回収期間を維持して集計以降を短縮する</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>調査対象者数が確定していない</t>
+          <t>村の実績データが29件中21件未受領</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>回収率の分母、管理番号の設計、手帳所持者数の将来推計の起点が定まらない</t>
+          <t>現行計画の評価、成果目標の現状値、見込量、給付費のいずれも確定できない</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>仕様書の約190人と現行計画の156人の差の理由を発送前に村へ確認する</t>
+          <t>最優先6件について9月末までの回答を求める。とくに年齢別・サービス別の匿名利用者一覧が個別積上げの前提となる</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>印刷仕様が仕様書と乖離している</t>
+          <t>調査票に国の標準項目3件が欠けている</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>部数・単価の精算根拠が定まらない</t>
+          <t>外出の目的（第4次障がい者計画の1指標が測定不能）、介護保険の利用状況（令和11年の高齢化率48.1％）、強度行動障害の該当有無（支援ニーズの母数が不明）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>仕様書はA4判・約24頁・黒1色の1種類だが実際は2種類。頁数・種類数・部数・単価の取扱いを村と協議し、結果を書面で残す</t>
+          <t>令和8年8月の国のマニュアルの標準項目。発送前でなければ追加できない。村は8月の朱書きで設問を削る方向の指示を出しているため、追加の可否を早急に協議する</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>1年以上長期入院者の実数が把握できていない</t>
+          <t>調査対象者数が確定していない</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>成果目標（２）の基盤整備量を告示別表第四の式で算定できない</t>
+          <t>回収率の分母、管理番号の設計、手帳所持者数の将来推計の起点が定まらない</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>村及び会津保健所へ照会中。ReMHRADで把握できるのは入院期間を問わない在院患者数までで、1年以上の内訳と年齢区分は公表データにない</t>
+          <t>仕様書の約190人と現行計画の156人の差の理由を発送前に村へ確認する</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>印刷仕様が仕様書と乖離している</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>部数・単価の精算根拠が定まらない</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>仕様書はA4判・約24頁・黒1色の1種類だが実際は2種類。頁数・種類数・部数・単価の取扱いを村と協議し、結果を書面で残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>1年以上長期入院者の実数が把握できていない</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>成果目標（２）の基盤整備量を告示別表第四の式で算定できない</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>村及び会津保健所へ照会中。ReMHRADで把握できるのは入院期間を問わない在院患者数までで、1年以上の内訳と年齢区分は公表データにない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>自立支援協議会の開催時期が未定</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>素案の合意時期が定まらず、パブリックコメント・印刷の日程も引けない</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>仕様書は開催1回程度を見込む。評価・素案・計画案の3段階を1回に集約する場合の構成を村と協議する</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>■ 直近のマイルストーン</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>時期</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>令和8年8月中</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>村の回答。既に期限を超過している</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>令和8年8〜9月</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>アンケートの発送・回収</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>上記3点の確定</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>令和8年9月</t>
+          <t>令和8年8月中</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>村実績データの受領（最優先6件）</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定、調査票への設問追加の可否</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>村の回答</t>
+          <t>村の回答。既に期限を超過している</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>令和8年10月</t>
+          <t>令和8年8〜9月</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>集計 → 現行計画の評価の確定</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>アンケートの発送・回収</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>アンケートの回収</t>
+          <t>上記3点の確定</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>令和8年11月</t>
+          <t>令和8年9月</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>見込量・成果目標・給付費の確定</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>村実績データの受領（最優先6件）</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>実績データの受領。算式は実装済み</t>
+          <t>村の回答</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>令和8年12月</t>
+          <t>令和8年10月</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>素案の確定、自立支援協議会</t>
+          <t>集計 → 現行計画の評価の確定</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -1110,19 +1093,19 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>開催時期が未定</t>
+          <t>アンケートの回収</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>令和9年1月</t>
+          <t>令和8年11月</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメント、調査結果報告書</t>
+          <t>見込量・成果目標・給付費の確定</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -1132,19 +1115,19 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>実績データの受領。算式は実装済み</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>令和9年2月</t>
+          <t>令和8年12月</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>意見への対応、原稿確定、組版</t>
+          <t>素案の確定、自立支援協議会</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -1154,27 +1137,71 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>パブコメの終了</t>
+          <t>開催時期が未定</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>令和9年1月</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメント、調査結果報告書</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>素案の確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>令和9年2月</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>意見への対応、原稿確定、組版</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>パブコメの終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>令和9年3月31日</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>納品（業務期間の末日）</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>全成果品の完成</t>
         </is>
@@ -1191,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1909,27 +1936,27 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>P3 統計分析</t>
+          <t>P2 基礎調査</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>人口・世帯の分析</t>
+          <t>実態調査及びPDCAサイクルに関するマニュアルの確認</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>住民基本台帳による人口の推移と、村公式推計による令和11年までの見通し</t>
+          <t>令和8年8月に国が改定したマニュアル（全81頁）を読み、調査票の標準項目・見込量の推計方法・PDCAサイクルの要求水準を成果物と突合</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)①</t>
+          <t>仕様書4-Ⅱ(1)</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1939,7 +1966,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -1956,11 +1983,11 @@
         <v>100</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_将来推計.xlsx。令和6年実績2,394人と令和11年公式推計の線形補間</t>
+          <t>確認結果（docs/北塩原村_実態調査PDCAマニュアル_確認結果.md）。別表第五の適用外判定が国の文書で裏付けられた。調査票の欠落3件（外出の目的・介護保険の利用状況・強度行動障害の該当有無）が国の標準項目であることを確認し、骨子案 第1章6・第5章1へ反映</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1977,22 +2004,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>障がい者手帳所持者数の将来推計</t>
+          <t>人口・世帯の分析</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>身体・療育・精神の3区分について3手法で推計し、予測区間と分母感度を検証</t>
+          <t>住民基本台帳による人口の推移と、村公式推計による令和11年までの見通し</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)①・4-Ⅱ(5)③</t>
+          <t>仕様書4-Ⅱ(3)①</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -2002,7 +2029,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -2019,16 +2046,16 @@
         <v>100</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_将来推計.xlsx（9シート）。骨子案修正版 第2章6として新設。県との比較シートで採用しなかった代替推計の理由も記録</t>
+          <t>北塩原村_将来推計.xlsx。令和6年実績2,394人と令和11年公式推計の線形補間</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>年齢階級別の手帳所持者数（未受領）により精度が上がる</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2067,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>給付実績の整理</t>
+          <t>障がい者手帳所持者数の将来推計</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>令和2〜7年度の介護給付費・障害児給付費をサービス別に整理</t>
+          <t>身体・療育・精神の3区分について3手法で推計し、予測区間と分母感度を検証</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(2)</t>
+          <t>仕様書4-Ⅱ(3)①・4-Ⅱ(5)③</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -2082,16 +2109,16 @@
         <v>100</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_障がいサービス給付実績_整理版（6シート）。サービス別内訳と年度合計が原票と一致することを検算済み</t>
+          <t>北塩原村_将来推計.xlsx（9シート）。骨子案修正版 第2章6として新設。県との比較シートで採用しなかった代替推計の理由も記録</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>年齢階級別の手帳所持者数（未受領）により精度が上がる</t>
         </is>
       </c>
     </row>
@@ -2103,22 +2130,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>圏域のサービス資源の把握</t>
+          <t>給付実績の整理</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ReMHRAD 障害福祉資源18サービスにより、会津北部4町村と近隣市の事業所数を確認</t>
+          <t>令和2〜7年度の介護給付費・障害児給付費をサービス別に整理</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)</t>
+          <t>仕様書4-Ⅱ(2)</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -2149,7 +2176,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_圏域サービス資源.xlsx（5シート）。村内に居宅介護1・重度訪問介護1・生活介護1を確認し、「本村には事業所がない」という記述を訂正</t>
+          <t>北塩原村_障がいサービス給付実績_整理版（6シート）。サービス別内訳と年度合計が原票と一致することを検算済み</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -2166,22 +2193,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>精神障がい者の地域移行に係る分析</t>
+          <t>圏域のサービス資源の把握</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>630調査・NDB精神医療指標・ReMHRAD により、県の平均生活日数・再入院率と村の在院者状況を把握</t>
+          <t>ReMHRAD 障害福祉資源18サービスにより、会津北部4町村と近隣市の事業所数を確認</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)⑤</t>
+          <t>仕様書4-Ⅱ(3)</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -2196,28 +2223,28 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J16" s="11" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>福島県_精神医療指標抽出.xlsx。別表第四のCを令和5年度630調査の2,591人で確定</t>
+          <t>北塩原村_圏域サービス資源.xlsx（5シート）。村内に居宅介護1・重度訪問介護1・生活介護1を確認し、「本村には事業所がない」という記述を訂正</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>令和7年度末時点の1年以上長期入院者の実数と年齢区分（村・会津保健所へ照会中）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2229,22 +2256,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>年齢階級別の分析</t>
+          <t>精神障がい者の地域移行に係る分析</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>身体は0〜17／18〜39／40〜64／65〜74／75歳以上、療育・精神は18歳未満／18〜64／65歳以上</t>
+          <t>630調査・NDB精神医療指標・ReMHRAD により、県の平均生活日数・再入院率と村の在院者状況を把握</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)①</t>
+          <t>仕様書4-Ⅱ(3)⑤</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -2254,80 +2281,80 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>推計の枠は作成済み（将来推計 05）</t>
+          <t>福島県_精神医療指標抽出.xlsx。別表第四のCを令和5年度630調査の2,591人で確定</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>年齢階級別の手帳所持者数・人口（村へ依頼中）</t>
+          <t>令和7年度末時点の1年以上長期入院者の実数と年齢区分（村・会津保健所へ照会中）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>P4 ニーズ調査</t>
+          <t>P3 統計分析</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>調査対象の抽出</t>
+          <t>年齢階級別の分析</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>身体約130人・精神約40人・療育約20人（計約190人）。抽出は委託者が行い、受託者にラベルシールとして提供</t>
+          <t>身体は0〜17／18〜39／40〜64／65〜74／75歳以上、療育・精神は18歳未満／18〜64／65歳以上</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(1)</t>
+          <t>仕様書4-Ⅱ(3)①</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>北塩原村</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J18" s="11" t="n">
@@ -2338,12 +2365,12 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>推計の枠は作成済み（将来推計 05）</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>仕様書の約190人と現行計画の156人（令和5年）の差の理由が未確認。回収率の分母・管理番号の設計に直結する</t>
+          <t>年齢階級別の手帳所持者数・人口（村へ依頼中）</t>
         </is>
       </c>
     </row>
@@ -2355,27 +2382,27 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>調査票の設計</t>
+          <t>調査対象の抽出</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>厚生労働省の調査項目及び村の過去調査を踏まえて設計し、委託者との協議の上決定</t>
+          <t>身体約130人・精神約40人・療育約20人（計約190人）。抽出は委託者が行い、受託者にラベルシールとして提供</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(2)</t>
+          <t>仕様書4-Ⅰ(1)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>北塩原村</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -2388,25 +2415,25 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>障がい者版52問・障がい児版51問。令和8年8月に村から朱書き修正指示40か所を受領し内容を確認済み（docs/北塩原村_アンケート調査票_村修正指示_確認結果.md）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>修正の反映は調査票担当。問36（就労選択支援）の削除は当方から再考を依頼中</t>
+          <t>仕様書の約190人と現行計画の156人（令和5年）の差の理由が未確認。回収率の分母・管理番号の設計に直結する</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2445,17 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>障がい特性に応じた配慮</t>
+          <t>調査票の設計</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>文字の大きさ・フォント・表現の工夫、ルビ等</t>
+          <t>厚生労働省の調査項目及び村の過去調査を踏まえて設計し、委託者との協議の上決定</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2460,16 +2487,16 @@
         <v>90</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>14pt程度・ルビ付与・白黒印刷・専門用語への短い解説（7月7日打合せで決定）。村からレスパイトケア・就労継続支援A型B型の用語説明の文言を受領</t>
+          <t>障がい者版52問・障がい児版51問。令和8年8月に村から朱書き修正指示40か所を受領し内容を確認済み（docs/北塩原村_アンケート調査票_村修正指示_確認結果.md）</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>最終レイアウトでの表示確認</t>
+          <t>修正の反映は調査票担当。問36（就労選択支援）の削除は当方から再考を依頼中。令和8年8月のマニュアルの標準項目との突合で、外出の目的・介護保険の利用状況・強度行動障害の該当有無の3件の欠落を確認。発送前の追加可否を村と協議する</t>
         </is>
       </c>
     </row>
@@ -2481,17 +2508,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>ウェブ回答用フォームの作成</t>
+          <t>障がい特性に応じた配慮</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>二次元コードを調査票又は依頼状に印字。紙・ウェブの重複回答を管理番号で管理</t>
+          <t>文字の大きさ・フォント・表現の工夫、ルビ等</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2520,19 +2547,19 @@
         </is>
       </c>
       <c r="J21" s="11" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Googleフォーム自動作成コード（1本統合分岐版）</t>
+          <t>14pt程度・ルビ付与・白黒印刷・専門用語への短い解説（7月7日打合せで決定）。村からレスパイトケア・就労継続支援A型B型の用語説明の文言を受領</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>枝番設問の選択肢順序の固定。調査票の修正指示の反映後に再生成が必要</t>
+          <t>最終レイアウトでの表示確認</t>
         </is>
       </c>
     </row>
@@ -2544,22 +2571,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>調査票・封筒の印刷</t>
+          <t>ウェブ回答用フォームの作成</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>調査票及び封筒（配布用・回収用）を各々必要部数印刷。仕様はA4判・約24ページ・黒1色</t>
+          <t>二次元コードを調査票又は依頼状に印字。紙・ウェブの重複回答を管理番号で管理</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(3)</t>
+          <t>仕様書4-Ⅰ(2)</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -2569,33 +2596,33 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>要対応</t>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>3</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>Googleフォーム自動作成コード（1本統合分岐版）</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>仕様書は約24頁の1種類だが実際は2種類。頁数・種類数・部数・単価の取扱いを村と協議する必要がある</t>
+          <t>枝番設問の選択肢順序の固定。調査票の修正指示の反映後に再生成が必要</t>
         </is>
       </c>
     </row>
@@ -2607,27 +2634,27 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>発送・回収管理</t>
+          <t>調査票・封筒の印刷</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宛名ラベルを配布用封筒に貼付し、調査票・返信用封筒を封入・封緘の上発送。発送及び回収に係る費用は受託者の負担</t>
+          <t>調査票及び封筒（配布用・回収用）を各々必要部数印刷。仕様はA4判・約24ページ・黒1色</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(4)</t>
+          <t>仕様書4-Ⅰ(3)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>受託者・北塩原村</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2637,7 +2664,7 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
@@ -2658,54 +2685,54 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>宛名ラベルの提供日が未定。郵送費は打合せで村が立替え後日実費精算とされ、仕様書の受託者負担と異なる運用のため書面確認が必要</t>
+          <t>仕様書は約24頁の1種類だが実際は2種類。頁数・種類数・部数・単価の取扱いを村と協議する必要がある</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>P5 集計・分析</t>
+          <t>P4 ニーズ調査</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>データ入力</t>
+          <t>発送・回収管理</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>厚生労働省が提示する集計ファイル様式を基本として入力</t>
+          <t>宛名ラベルを配布用封筒に貼付し、調査票・返信用封筒を封入・封緘の上発送。発送及び回収に係る費用は受託者の負担</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(5)</t>
+          <t>仕様書4-Ⅰ(4)</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・北塩原村</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="J24" s="11" t="n">
@@ -2721,7 +2748,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>アンケートの回収。集計様式の準備</t>
+          <t>宛名ラベルの提供日が未定。郵送費は打合せで村が立替え後日実費精算とされ、仕様書の受託者負担と異なる運用のため書面確認が必要</t>
         </is>
       </c>
     </row>
@@ -2733,22 +2760,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>集計・分析の設計</t>
+          <t>データ入力</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>基本集計及び年齢・障がい種別等によるクロス集計。少数母数の取扱い</t>
+          <t>厚生労働省が提示する集計ファイル様式を基本として入力</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(6)</t>
+          <t>仕様書4-Ⅰ(5)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2758,7 +2785,7 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -2766,25 +2793,25 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>アンケート集計分析方法（少数母数対応・計画接続メモ）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>小規模公表基準（n&lt;5の秘匿、地区別・障がい種別クロスの扱い）を村と合意する</t>
+          <t>アンケートの回収。集計様式の準備</t>
         </is>
       </c>
     </row>
@@ -2796,17 +2823,17 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>自由回答の取りまとめ</t>
+          <t>集計・分析の設計</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>自由記述の分類・要約。村の修正指示により問11-2・問37-2の自由記述欄が新設される</t>
+          <t>基本集計及び年齢・障がい種別等によるクロス集計。少数母数の取扱い</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2821,33 +2848,33 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>アンケート集計分析方法（少数母数対応・計画接続メモ）</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>アンケートの回収</t>
+          <t>小規模公表基準（n&lt;5の秘匿、地区別・障がい種別クロスの扱い）を村と合意する</t>
         </is>
       </c>
     </row>
@@ -2859,22 +2886,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>成果目標との紐付け</t>
+          <t>自由回答の取りまとめ</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>現行計画は成果目標の設定根拠に調査結果報告書の頁番号を引用している。第8期でも同じ構造とするため、集計段階で設問と成果目標を紐付ける</t>
+          <t>自由記述の分類・要約。村の修正指示により問11-2・問37-2の自由記述欄が新設される</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)⑤</t>
+          <t>仕様書4-Ⅰ(6)</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2905,12 +2932,12 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>現行計画評価 02_成果目標の評価に引用関係を整理済み</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>アンケートの集計</t>
+          <t>アンケートの回収</t>
         </is>
       </c>
     </row>
@@ -2922,22 +2949,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>調査結果報告書の作成</t>
+          <t>成果目標との紐付け</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>設問ごとにグラフを作成し、分析結果を報告書として取りまとめる</t>
+          <t>現行計画は成果目標の設定根拠に調査結果報告書の頁番号を引用している。第8期でも同じ構造とするため、集計段階で設問と成果目標を紐付ける</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(7)・成果品②</t>
+          <t>仕様書4-Ⅱ(3)⑤</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -2947,12 +2974,12 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
           <t>2026-11</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>2026-12</t>
         </is>
       </c>
       <c r="I28" s="16" t="inlineStr">
@@ -2964,43 +2991,43 @@
         <v>0</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>現行計画評価 02_成果目標の評価に引用関係を整理済み</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>集計の完了</t>
+          <t>アンケートの集計</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>P6 現行計画の評価</t>
+          <t>P5 集計・分析</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>サービス利用実績の評価</t>
+          <t>調査結果報告書の作成</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>令和3〜5年度の見込量と実績を全数突合し、乖離の類型を判定</t>
+          <t>設問ごとにグラフを作成し、分析結果を報告書として取りまとめる</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(2)</t>
+          <t>仕様書4-Ⅰ(7)・成果品②</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -3010,33 +3037,33 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_現行計画評価.xlsx（7シート）。サービス25区分・地域生活支援事業16事業。計上漏れ・過大計上を特定</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>集計の完了</t>
         </is>
       </c>
     </row>
@@ -3048,17 +3075,17 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>成果目標の達成状況の評価</t>
+          <t>サービス利用実績の評価</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>第7期の成果目標7区分の現状値・目標値・設定根拠と評価の見通し</t>
+          <t>令和3〜5年度の見込量と実績を全数突合し、乖離の類型を判定</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -3078,28 +3105,28 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J30" s="11" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K30" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>現行計画評価 02_成果目標の評価。令和8年8月の村の朱書きにより基幹相談支援センター未設置・セルフプラン率0％・医療的ケア児1人を確定</t>
+          <t>北塩原村_現行計画評価.xlsx（7シート）。サービス25区分・地域生活支援事業16事業。計上漏れ・過大計上を特定</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>令和6・7年度の実績と令和8年度見込（村へ依頼中）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3111,17 +3138,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>活動指標の達成状況の評価</t>
+          <t>成果目標の達成状況の評価</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>第7期の活動指標の実績。第8期は83項目のうち本村分65項目</t>
+          <t>第7期の成果目標7区分の現状値・目標値・設定根拠と評価の見通し</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3136,12 +3163,12 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
@@ -3150,19 +3177,19 @@
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_活動指標.xlsx（4シート）で第8期の設定は完了</t>
+          <t>現行計画評価 02_成果目標の評価。令和8年8月の村の朱書きにより基幹相談支援センター未設置・セルフプラン率0％・医療的ケア児1人を確定</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の活動指標実績（村へ依頼中）</t>
+          <t>令和6・7年度の実績と令和8年度見込（村へ依頼中）</t>
         </is>
       </c>
     </row>
@@ -3174,22 +3201,22 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標値の測定</t>
+          <t>活動指標の達成状況の評価</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>8指標の測定手段を確認し、アンケートで測るもの・行政データで測るものを区分</t>
+          <t>第7期の活動指標の実績。第8期は83項目のうち本村分65項目</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(2)・4-Ⅱ(5)②</t>
+          <t>仕様書4-Ⅱ(2)</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -3199,60 +3226,60 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J32" s="11" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>現行計画評価 の施策指標8件。測定可能6・測定不能1・要確認1。外出目的の設問が調査票に無く1指標が測定できないことを特定</t>
+          <t>北塩原村_活動指標.xlsx（4シート）で第8期の設定は完了</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>令和6年度の活動指標実績（村へ依頼中）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>P7 推計・見込量</t>
+          <t>P6 現行計画の評価</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>推計方法の確定</t>
+          <t>第4次障がい者計画の施策目標値の測定</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>個別積上げ方式（実績・意向・心身の状況を利用者単位で積み上げる方法）。別表第五の適用判定を含む</t>
+          <t>8指標の測定手段を確認し、アンケートで測るもの・行政データで測るものを区分</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)</t>
+          <t>仕様書4-Ⅱ(2)・4-Ⅱ(5)②</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3279,11 +3306,11 @@
         <v>100</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_サービス見込量.xlsx（13シート）。11_告示別表第一根拠・12_別表第五判定。全域過疎により別表第五は適用対象外と確定し、個別積上げ方式を採用</t>
+          <t>現行計画評価 の施策指標8件。測定可能6・測定不能1・要確認1。外出目的の設問が調査票に無く1指標が測定できないことを特定</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -3300,22 +3327,22 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>障がい福祉サービスの見込量の推計</t>
+          <t>推計方法の確定</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>介護給付・訓練等給付の利用者数と量。年齢到達に伴う移行を含む</t>
+          <t>個別積上げ方式（実績・意向・心身の状況を利用者単位で積み上げる方法）。別表第五の適用判定を含む</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)②</t>
+          <t>仕様書4-Ⅱ(3)</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -3330,28 +3357,28 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J34" s="11" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="K34" s="11" t="n">
         <v>5</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>算式は実装済み（02〜04）。障害支援区分別人数15人による検証を実施し、既存の見込量と矛盾しないことを確認</t>
+          <t>北塩原村_サービス見込量.xlsx（13シート）。11_告示別表第一根拠・12_別表第五判定。全域過疎により別表第五は適用対象外と確定し、個別積上げ方式を採用</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>年齢別・サービス別の匿名利用者一覧、サービス別の支給決定者数（村へ依頼中）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3363,22 +3390,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>障がい児通所支援等の見込量の推計</t>
+          <t>障がい福祉サービスの見込量の推計</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>児童発達支援・放課後等デイサービス等の利用者数と量</t>
+          <t>介護給付・訓練等給付の利用者数と量。年齢到達に伴う移行を含む</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)③</t>
+          <t>仕様書4-Ⅱ(3)②</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3402,19 +3429,19 @@
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>算式は実装済み（04）。障がい児入所0件・通所支援の申請中0件を村の朱書きで確認</t>
+          <t>算式は実装済み（02〜04）。障害支援区分別人数15人による検証を実施し、既存の見込量と矛盾しないことを確認</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>令和6・7年度の障害児給付費の変動理由（児童発達支援23件→1件、放課後等デイ12件→27件）の確認</t>
+          <t>年齢別・サービス別の匿名利用者一覧、サービス別の支給決定者数（村へ依頼中）</t>
         </is>
       </c>
     </row>
@@ -3426,22 +3453,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量の推計</t>
+          <t>障がい児通所支援等の見込量の推計</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>必須15事業・任意3事業の事業ごとの実施に関する考え方と量の見込み</t>
+          <t>児童発達支援・放課後等デイサービス等の利用者数と量</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)④</t>
+          <t>仕様書4-Ⅱ(3)③</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -3456,28 +3483,28 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J36" s="11" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K36" s="11" t="n">
         <v>3</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_地域生活支援事業.xlsx（4シート）。告示第三の二の3の4事項に対応</t>
+          <t>算式は実装済み（04）。障がい児入所0件・通所支援の申請中0件を村の朱書きで確認</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>移動支援0人・福祉ホームの実績と見込の逆転など、確認事項7件が未解消</t>
+          <t>令和6・7年度の障害児給付費の変動理由（児童発達支援23件→1件、放課後等デイ12件→27件）の確認</t>
         </is>
       </c>
     </row>
@@ -3489,22 +3516,22 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>地域生活支援事業の見込量の推計</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>第8期の成果目標8区分（人材確保・定着が新設）</t>
+          <t>必須15事業・任意3事業の事業ごとの実施に関する考え方と量の見込み</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)⑤</t>
+          <t>仕様書4-Ⅱ(3)④</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3519,28 +3546,28 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版 第4章。国基準数値を告示本文と照合済み。村の朱書きにより（３）（４）（６）を具体化</t>
+          <t>北塩原村_地域生活支援事業.xlsx（4シート）。告示第三の二の3の4事項に対応</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>令和7年度末の施設入所者数、令和6年度の一般就労移行実績、1年以上長期入院者の実数</t>
+          <t>移動支援0人・福祉ホームの実績と見込の逆転など、確認事項7件が未解消</t>
         </is>
       </c>
     </row>
@@ -3552,17 +3579,17 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>7-6</t>
+          <t>7-5</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>活動指標の設定</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>別表第一の83項目から本村で設定する65項目を選定。告示第三の四㈡により見込量以外の活動指標は任意</t>
+          <t>第8期の成果目標8区分（人材確保・定着が新設）</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3582,28 +3609,28 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J38" s="11" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_活動指標.xlsx。設定51・検討7・設定しない7・都道府県指標18</t>
+          <t>骨子案修正版 第4章。国基準数値を告示本文と照合済み。村の朱書きにより（３）（４）（６）を具体化</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>令和6年度実績の受領後に現状値を入れる</t>
+          <t>令和7年度末の施設入所者数、令和6年度の一般就労移行実績、1年以上長期入院者の実数</t>
         </is>
       </c>
     </row>
@@ -3615,22 +3642,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>7-6</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>給付費・財源構成の推計</t>
+          <t>活動指標の設定</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>サービス別の給付費と、国1/2・県1/4・村1/4の法定負担による財源構成</t>
+          <t>別表第一の83項目から本村で設定する65項目を選定。告示第三の四㈡により見込量以外の活動指標は任意</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)</t>
+          <t>仕様書4-Ⅱ(3)⑤</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3645,55 +3672,55 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_財源構成案.xlsx。年間給付費＝利用者数×単価×12×改定率で算式化。令和8・9年度の報酬改定率をパラメータ化済み</t>
+          <t>北塩原村_活動指標.xlsx。設定51・検討7・設定しない7・都道府県指標18</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>見込量の確定、障がい福祉関係の歳入歳出決算（村へ依頼中）</t>
+          <t>令和6年度実績の受領後に現状値を入れる</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>P8 施策検討・計画案</t>
+          <t>P7 推計・見込量</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>障がい者福祉施策の検討</t>
+          <t>給付費・財源構成の推計</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>現行計画の成果と課題を踏まえ、次期計画に盛り込む施策を検討</t>
+          <t>サービス別の給付費と、国1/2・県1/4・村1/4の法定負担による財源構成</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(4)</t>
+          <t>仕様書4-Ⅱ(3)</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -3711,25 +3738,25 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J40" s="11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K40" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版 第3章（基本理念・基本目標及び施策体系）。第8期で加わる視点と施策体系の対応表を新設</t>
+          <t>北塩原村_財源構成案.xlsx。年間給付費＝利用者数×単価×12×改定率で算式化。令和8・9年度の報酬改定率をパラメータ化済み</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>現行計画の評価の確定</t>
+          <t>見込量の確定、障がい福祉関係の歳入歳出決算（村へ依頼中）</t>
         </is>
       </c>
     </row>
@@ -3741,22 +3768,22 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>障がい者福祉施策の検討</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>仕様書が定める記載事項8項目（基本理念・施策体系・手帳所持者数の将来推計・サービス見込量・障がい児通所支援等の見込量・地域生活支援事業の見込量・成果目標及び活動指標・推進体制及び進行管理）</t>
+          <t>現行計画の成果と課題を踏まえ、次期計画に盛り込む施策を検討</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(5)</t>
+          <t>仕様書4-Ⅱ(4)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3766,12 +3793,12 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -3780,19 +3807,19 @@
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版（全8章・97表・369段落・図9点）。推計方法・年齢到達移行・活動指標・財源構成の4節を新設</t>
+          <t>骨子案修正版 第3章（基本理念・基本目標及び施策体系）。第8期で加わる視点と施策体系の対応表を新設</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>アンケート結果、実績データ、見込量の確定</t>
+          <t>現行計画の評価の確定</t>
         </is>
       </c>
     </row>
@@ -3804,17 +3831,17 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>確保のための方策の記載</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小規模町村・中山間地域向けの確保方策。介護保険事業所への指定働きかけ、共生型サービス、基準該当、多機能型・従たる事業所、短期入所</t>
+          <t>仕様書が定める記載事項8項目（基本理念・施策体系・手帳所持者数の将来推計・サービス見込量・障がい児通所支援等の見込量・地域生活支援事業の見込量・成果目標及び活動指標・推進体制及び進行管理）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -3829,33 +3856,33 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J42" s="11" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版 第5章8。告示が名指しする5つの具体策を反映し、圏域の事業所数を原典から表として生成する方式に変更</t>
+          <t>骨子案修正版（全8章・97表・369段落・図9点）。推計方法・年齢到達移行・活動指標・財源構成の4節を新設</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>アンケート結果、実績データ、見込量の確定</t>
         </is>
       </c>
     </row>
@@ -3867,22 +3894,22 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>分量配分の設計</t>
+          <t>確保のための方策の記載</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>成果品①は約60頁。章別の目標頁数を先に決め、原稿段階で収める</t>
+          <t>小規模町村・中山間地域向けの確保方策。介護保険事業所への指定働きかけ、共生型サービス、基準該当、多機能型・従たる事業所、短期入所</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品①</t>
+          <t>仕様書4-Ⅱ(5)</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3909,11 +3936,11 @@
         <v>100</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>計画書_分量配分計画（docs）。現行63頁の章別配分を基準に60頁へ配分。削減順序と削ってはならないものを明記</t>
+          <t>骨子案修正版 第5章8。告示が名指しする5つの具体策を反映し、圏域の事業所数を原典から表として生成する方式に変更</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
@@ -3925,27 +3952,27 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P8 施策検討・計画案</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>自立支援協議会の資料作成</t>
+          <t>分量配分の設計</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>委託者が協議会に報告・説明し、受託者は会議資料の作成、会議への出席、会議記録（要旨）の作成等の運営支援を行う。開催は1回程度</t>
+          <t>成果品①は約60頁。章別の目標頁数を先に決め、原稿段階で収める</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(7)</t>
+          <t>仕様書5 成果品①</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -3960,28 +3987,28 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J44" s="11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>会議資料5点を作成（協議会資料1・2・8、庁議資料2・4）。村資料に依存しない資料を先行して整備</t>
+          <t>計画書_分量配分計画（docs）。現行63頁の章別配分を基準に60頁へ配分。削減順序と削ってはならないものを明記</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>協議会の開催時期が未定。委員名簿が未受領</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3993,17 +4020,17 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>協議会の開催</t>
+          <t>自立支援協議会の資料作成</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>調査結果・素案・計画案の報告と審議</t>
+          <t>委託者が協議会に報告・説明し、受託者は会議資料の作成、会議への出席、会議記録（要旨）の作成等の運営支援を行う。開催は1回程度</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -4013,38 +4040,38 @@
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>北塩原村・受託者</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>会議資料5点を作成（協議会資料1・2・8、庁議資料2・4）。村資料に依存しない資料を先行して整備</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>開催日が未定。素案の確定</t>
+          <t>協議会の開催時期が未定。委員名簿が未受領</t>
         </is>
       </c>
     </row>
@@ -4056,22 +4083,22 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>庁議の開催</t>
+          <t>協議会の開催</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>庁内各課との調整。関連計画との整合と依頼事項</t>
+          <t>調査結果・素案・計画案の報告と審議</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>仕様書4-Ⅱ(7)</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr">
@@ -4081,12 +4108,12 @@
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="I46" s="16" t="inlineStr">
@@ -4098,16 +4125,16 @@
         <v>0</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>庁議資料2点は作成済み</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>開催時期が未定</t>
+          <t>開催日が未定。素案の確定</t>
         </is>
       </c>
     </row>
@@ -4119,22 +4146,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>庁議の開催</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>計画案について意見を募集し、得られた意見を反映</t>
+          <t>庁内各課との調整。関連計画との整合と依頼事項</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(6)</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4144,12 +4171,12 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
           <t>2027-01</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>2027-02</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
@@ -4161,16 +4188,16 @@
         <v>0</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>庁議資料2点は作成済み</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>素案の確定。実施時期が未定</t>
+          <t>開催時期が未定</t>
         </is>
       </c>
     </row>
@@ -4182,17 +4209,17 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>意見の整理、対応案の作成、計画への反映</t>
+          <t>計画案について意見を募集し、得られた意見を反映</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -4202,12 +4229,12 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>北塩原村・受託者</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -4233,29 +4260,29 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>素案の確定。実施時期が未定</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>計画書の原稿確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>協議会・パブリックコメントを経て得られた意見を反映の上、最終的に取りまとめる</t>
+          <t>意見の整理、対応案の作成、計画への反映</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -4287,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
@@ -4296,7 +4323,7 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
     </row>
@@ -4308,22 +4335,22 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>10-2</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>レイアウト・組版</t>
+          <t>計画書の原稿確定</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>A4判・両面・約60頁・モノクロ</t>
+          <t>協議会・パブリックコメントを経て得られた意見を反映の上、最終的に取りまとめる</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品①</t>
+          <t>仕様書4-Ⅱ(6)</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr">
@@ -4338,7 +4365,7 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="I50" s="16" t="inlineStr">
@@ -4354,12 +4381,12 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>分量配分計画を作成済み。実際の組版で1頁あたりの文字数を実測し補正する</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>原稿の確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4371,17 +4398,17 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-2</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>校正</t>
+          <t>レイアウト・組版</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>村の確認を経て校了</t>
+          <t>A4判・両面・約60頁・モノクロ</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -4391,12 +4418,12 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>受託者・北塩原村</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -4413,16 +4440,16 @@
         <v>0</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>分量配分計画を作成済み。実際の組版で1頁あたりの文字数を実測し補正する</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>原稿の確定</t>
         </is>
       </c>
     </row>
@@ -4434,27 +4461,27 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>校正</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>計画書はコピー・くるみ製本30部、調査報告書はコピー・ホチキス製本10部</t>
+          <t>村の確認を経て校了</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品①②</t>
+          <t>仕様書5 成果品①</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・北塩原村</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
@@ -4485,7 +4512,7 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>校了。印刷業者の手配</t>
+          <t>組版</t>
         </is>
       </c>
     </row>
@@ -4497,22 +4524,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>電子媒体の作成</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>計画書と調査報告書の電子データ一式</t>
+          <t>計画書はコピー・くるみ製本30部、調査報告書はコピー・ホチキス製本10部</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品③</t>
+          <t>仕様書5 成果品①②</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4539,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
@@ -4548,7 +4575,7 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>編集可能形式とPDFの別を村に確認する</t>
+          <t>校了。印刷業者の手配</t>
         </is>
       </c>
     </row>
@@ -4560,27 +4587,27 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>電子媒体の作成</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>令和9年3月31日まで</t>
+          <t>計画書と調査報告書の電子データ一式</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>仕様書3（業務期間）</t>
+          <t>仕様書5 成果品③</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>受託者・北塩原村</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -4611,12 +4638,75 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
+          <t>編集可能形式とPDFの別を村に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>P10 完成・納品</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>納品・検収</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>令和9年3月31日まで</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>仕様書3（業務期間）</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>受託者・北塩原村</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
           <t>全成果品の完成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4707,31 +4797,31 @@
         </is>
       </c>
       <c r="B2" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A2)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A2,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A2,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A2,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A2,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A2,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A2)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A2)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A2)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A2)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A2)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A2)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I2" s="11" t="inlineStr">
@@ -4757,31 +4847,31 @@
         </is>
       </c>
       <c r="B3" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A3)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A3,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A3,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A3,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A3,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A3,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A3)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A3)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A3)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A3)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A3)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A3)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -4796,7 +4886,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>―（国の基本指針は令和8年3月31日に告示済みで確定）</t>
+          <t>―（基本指針は令和8年3月31日告示、実態調査PDCAマニュアルは同年8月改定。いずれも確認済み）</t>
         </is>
       </c>
     </row>
@@ -4807,31 +4897,31 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A4)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A4,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A4,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A4,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A4,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A4,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A4)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A4)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A4)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A4)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A4)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A4)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -4857,31 +4947,31 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A5)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A5,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A5,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A5,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A5,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A5,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A5)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A5)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A5)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A5)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A5)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A5)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -4907,31 +4997,31 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A6)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A6,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A6,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A6,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A6,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A6,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A6)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A6)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A6)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A6)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A6)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A6)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -4957,31 +5047,31 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A7)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A7,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A7,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A7,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A7,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A7,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A7)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A7)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A7)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A7)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A7)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A7)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -5007,31 +5097,31 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A8)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A8,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A8,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A8,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A8,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A8,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A8)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A8)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A8)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A8)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A8)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A8)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -5057,31 +5147,31 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A9)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A9,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A9,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A9,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A9,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A9,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A9)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A9)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A9)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A9)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A9)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A9)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -5107,31 +5197,31 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A10)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A10,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A10,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A10,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A10,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A10,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A10)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A10)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A10)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A10)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A10)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A10)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -5157,31 +5247,31 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$54,$A11)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A11,'01_WBS'!$I$2:$I$54,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"完了")</f>
         <v/>
       </c>
       <c r="D11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A11,'01_WBS'!$I$2:$I$54,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"進行中")</f>
         <v/>
       </c>
       <c r="E11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A11,'01_WBS'!$I$2:$I$54,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"要対応")</f>
         <v/>
       </c>
       <c r="F11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A11,'01_WBS'!$I$2:$I$54,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
         <v/>
       </c>
       <c r="G11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$54,$A11,'01_WBS'!$I$2:$I$54,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"未着手")</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A11)*'01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A11)*'01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT(('01_WBS'!$A$2:$A$54=$A11)*'01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A11)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A11)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A11)*'01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -5231,7 +5321,7 @@
         <v/>
       </c>
       <c r="H12" s="19">
-        <f>IF(SUMPRODUCT('01_WBS'!$K$2:$K$54)=0,0,SUMPRODUCT('01_WBS'!$J$2:$J$54*'01_WBS'!$K$2:$K$54)/SUMPRODUCT('01_WBS'!$K$2:$K$54)/100)</f>
+        <f>IF(SUMPRODUCT('01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT('01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT('01_WBS'!$K$2:$K$55)/100)</f>
         <v/>
       </c>
       <c r="I12" s="18" t="inlineStr">
@@ -5509,7 +5599,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定</t>
+          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定、調査票への設問追加の可否（外出の目的・介護保険・強度行動障害）</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -5524,7 +5614,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>アンケート発送のクリティカルパス。3点とも未了</t>
+          <t>アンケート発送のクリティカルパス。いずれも未了。設問追加は令和8年8月の国のマニュアルの標準項目に関するもので、発送前でなければ対応できない</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6506,7 +6596,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>アンケート調査票への村の修正指示</t>
+          <t>実態調査及びPDCAサイクルに関するマニュアル（令和8年8月）</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -6522,19 +6612,19 @@
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている／反映先：村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果／希望期限：2026-08-14</t>
+          <t>【受領済み】福島県通知（8生福第2646号・8こ第2041号 令和8年8月24日）により受領。厚労省・こども家庭庁の令和8年8月19日事務連絡の別添。全81頁。令和2年版を基本指針の改正を踏まえて修正したもの／反映先：サービス見込量 12_別表第五判定／骨子案修正版 第1章6・第5章1／北塩原村_実態調査PDCAマニュアル_確認結果／希望期限：2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>PDCAの評価体制・スケジュール・公表方法</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -6550,19 +6640,19 @@
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>関連計画との整合確認／反映先：計画本文 第1章・第7章／希望期限：2026-10-31</t>
+          <t>自立支援協議会と庁内会議体の役割分担、実績把握と評価の時期（村の予算編成に合わせる）、中間評価の結果の公表方法（ホームページ・広報誌・協議会資料の公開範囲）／反映先：骨子案修正版 第1章6／希望期限：2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>アンケート調査票への村の修正指示</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -6570,15 +6660,15 @@
           <t>北塩原村</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無／反映先：サービス見込量 02／希望期限：2026-10-31</t>
+          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている／反映先：村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果／希望期限：2026-08-14</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6680,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>自立支援協議会の委員名簿</t>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -6606,12 +6696,68 @@
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
+          <t>関連計画との整合確認／反映先：計画本文 第1章・第7章／希望期限：2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無／反映先：サービス見込量 02／希望期限：2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>自立支援協議会の委員名簿</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>任期・氏名・所属・役職／反映先：計画書 資料編／希望期限：2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>※ No 列は優先度。依頼の詳細は 北塩原村_業務進捗管理.xlsx 04_村資料受領状況 を参照。</t>
         </is>
@@ -6810,7 +6956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7277,22 +7423,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>障がい者票に介護保険・65歳到達に関する設問がない</t>
+          <t>障がい者票に介護保険・65歳到達に関する設問がない（国の標準項目）</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない</t>
+          <t>令和11年の高齢化率が48.1%となる村で、65歳前後の実態を把握する手段がない。令和8年8月のマニュアルの調査票ひな型は問37（介護保険の利用）・問38（要介護度）・問39（利用している介護保険サービス）の3問を標準項目として置いている。同マニュアルは身体障害者の73%が65歳以上であることを踏まえ、18歳未満／18〜64歳／65歳以上の年齢階層別に分析する例を示している</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>調査設計／影響度中</t>
+          <t>調査設計／影響度高</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳での確認に一本化する</t>
+          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳と介護保険の認定情報の突合に一本化する</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -7309,12 +7455,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標のうち1指標が測定できない</t>
+          <t>外出目的の設問がなく、第4次障がい者計画の1指標が測定できない（国の標準項目）</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない</t>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1%→40%）」について、前回調査にあった外出目的の設問が0728調査票にない。令和8年8月のマニュアルは図表6で「外出の目的」を主な調査項目に掲げ、「外出支援のために必要となる施策等の検討に利用」するとしている（調査票ひな型では問26）。移動支援・同行援護の見込量根拠にも直結する</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -7432,30 +7578,94 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>R-20</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>強度行動障害の該当有無を聞く設問がなく、支援ニーズの母数が特定できない</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>調査票は問20で「強度行動障がい支援に関して必要だと思う支援」を聞くが、回答者本人が該当するかを聞いていない。令和8年8月のマニュアルの調査票ひな型は問16で「強度行動障害があると言われたことはありますか」を置き、重度障害者の支援ニーズを把握するクロス集計を示している。第8期基本指針は強度行動障害を有する者の支援ニーズ把握を新規の視点としている</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>調査設計／影響度中</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>発送前であれば設問を追加する。追加しない場合は、村の朱書きで判明した区分6の2人について行動関連項目の点数を確認する（既に照会中）</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>R-21</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>障害支援区分の削除は国の標準項目を落とすことになる</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>村は問7の削除を指示し、当方は対象者15人という規模から削除に異議なしと回答した。一方、令和8年8月のマニュアルは障害支援区分をクロス集計の項目として明示し（P.12）、調査票ひな型でも問35に置いている。ただし同マニュアル自身が、調査対象者数が少ない場合は標本誤差が大きくなるため集計結果の解釈を慎重に行う必要があるとしている</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>調査設計／影響度中</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>国の標準項目である旨を村へ伝えたうえで最終判断をいただく。当方の見解は変わらず、削除でも支障はない（区分別人数は役場データで把握済み）</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
           <t>R-19</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>障がい児版の設問番号に誤りがある</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>問11の選択肢番号「13」が2つある（「自傷、他害、強いこだわり、パニックなどへの対応」と「特にない」）。問10の選択肢番号は「3」が欠番。いずれも村の朱書きとは別に、通読して気づいたもの</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>調査設計／影響度低</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>調査票担当へ申し送り済み。印刷前に番号を振り直す。問10は問8との統合指示があるため、統合時に整理する</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
@@ -7472,7 +7682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7697,36 +7907,66 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>国のマニュアルの改定</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月に「障害福祉計画策定に係る実態調査及びPDCAサイクルに関するマニュアル」が改定され、福島県から市町村へ通知された。調査票の標準項目と、見込量推計・PDCAサイクルの要求水準が示された</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>厚労省・こども家庭庁 令和8年8月19日事務連絡／福島県 8生福第2646号・8こ第2041号 令和8年8月24日</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>確認結果を文書化済み。別表第五の適用外判定は裏付けられた。調査票の欠落3件について発送前に村と協議する必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>調査票の修正指示</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に村から朱書き40か所の修正指示を受領。うち9件は削除理由として村の実データが書き添えられていた</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>仕様書4-Ⅰ(2)（委託者との協議の上決定）</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>確認結果を文書化済み（docs/北塩原村_アンケート調査票_村修正指示_確認結果.md）。問36の削除について再考を依頼中</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>※ 仕様書6(3)により北塩原村委託契約約款に準拠する。仕様書と異なる運用は書面で記録を残す。</t>
         </is>

--- a/output/北塩原村_業務進捗管理表.xlsx
+++ b/output/北塩原村_業務進捗管理表.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_変更管理・打合せ記録" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$M$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$M$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -807,239 +807,224 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>同月、国が「障害福祉計画策定に係る実態調査及びPDCAサイクルに関するマニュアル」を改定し、福島県から市町村へ通知された（8生福第2646号・8こ第2041号）。全81頁を読み、成果物と突合した。別表第五を適用しないという当方の判定は国の文書で裏付けられた一方、調査票に国の標準項目3件（外出の目的・介護保険の利用状況・強度行動障害の該当有無）が欠けていることが確認された。いずれも発送前でなければ対応できない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+          <t>同月、国が「障害福祉計画策定に係る実態調査及びPDCAサイクルに関するマニュアル」を改定し、福島県から市町村へ通知された（8生福第2646号・8こ第2041号）。全81頁を読み、成果物と突合した。別表第五を適用しないという当方の判定は国の文書で裏付けられた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>調査票は8月25日版で確定した。マニュアルの発出（8月19日事務連絡）と確定の時期が重なったため、標準項目のうち外出の目的・介護保険の利用状況・強度行動障害の該当有無・障害支援区分の4件が確定版にない。クロス集計25件と行政データとの突合6件を設計し、うち3件は代替の目処が立った。残る1件（外出の目的）は第4次障がい者計画の指標に関わるため村との再協議を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>■ 警戒事項</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>アンケートの発送が工程案の令和8年8月上旬に間に合わない</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>回収期間または集計期間が圧縮され、報告書・計画書の工程に波及する</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>印刷仕様を確定し、宛名ラベルの提供日を村と合意する。遅延が確定した場合は回収期間を維持して集計以降を短縮する</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>村の実績データが29件中21件未受領</t>
+          <t>アンケートの発送が工程案の令和8年8月上旬に間に合わない</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>現行計画の評価、成果目標の現状値、見込量、給付費のいずれも確定できない</t>
+          <t>回収期間または集計期間が圧縮され、報告書・計画書の工程に波及する</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>最優先6件について9月末までの回答を求める。とくに年齢別・サービス別の匿名利用者一覧が個別積上げの前提となる</t>
+          <t>印刷仕様を確定し、宛名ラベルの提供日を村と合意する。遅延が確定した場合は回収期間を維持して集計以降を短縮する</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>調査票に国の標準項目3件が欠けている</t>
+          <t>村の実績データが29件中21件未受領</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>外出の目的（第4次障がい者計画の1指標が測定不能）、介護保険の利用状況（令和11年の高齢化率48.1％）、強度行動障害の該当有無（支援ニーズの母数が不明）</t>
+          <t>現行計画の評価、成果目標の現状値、見込量、給付費のいずれも確定できない</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月の国のマニュアルの標準項目。発送前でなければ追加できない。村は8月の朱書きで設問を削る方向の指示を出しているため、追加の可否を早急に協議する</t>
+          <t>最優先6件について9月末までの回答を求める。とくに年齢別・サービス別の匿名利用者一覧が個別積上げの前提となる</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>調査対象者数が確定していない</t>
+          <t>第4次障がい者計画の1指標が測定できない</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>回収率の分母、管理番号の設計、手帳所持者数の将来推計の起点が定まらない</t>
+          <t>「外出目的が趣味・スポーツ・グループ活動である人の割合（28.1％→40％）」。確定版に外出の目的を問う設問がなく、最も近い問42は意向のため前回値と接続できない</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>仕様書の約190人と現行計画の156人の差の理由を発送前に村へ確認する</t>
+          <t>指標の測定方法の変更は改定対象外の計画に関わる村の判断事項。代理指標（問42で趣味・スポーツ等を選んだ割合）への切替えを提案し、村と再協議する（クロス集計設計 S-1）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>印刷仕様が仕様書と乖離している</t>
+          <t>調査対象者数が確定していない</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>部数・単価の精算根拠が定まらない</t>
+          <t>回収率の分母、管理番号の設計、手帳所持者数の将来推計の起点が定まらない</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>仕様書はA4判・約24頁・黒1色の1種類だが実際は2種類。頁数・種類数・部数・単価の取扱いを村と協議し、結果を書面で残す</t>
+          <t>仕様書の約190人と現行計画の156人の差の理由を発送前に村へ確認する</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>1年以上長期入院者の実数が把握できていない</t>
+          <t>印刷仕様が仕様書と乖離している</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>成果目標（２）の基盤整備量を告示別表第四の式で算定できない</t>
+          <t>部数・単価の精算根拠が定まらない</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>村及び会津保健所へ照会中。ReMHRADで把握できるのは入院期間を問わない在院患者数までで、1年以上の内訳と年齢区分は公表データにない</t>
+          <t>仕様書はA4判・約24頁・黒1色の1種類だが実際は2種類。頁数・種類数・部数・単価の取扱いを村と協議し、結果を書面で残す</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>1年以上長期入院者の実数が把握できていない</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>成果目標（２）の基盤整備量を告示別表第四の式で算定できない</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>村及び会津保健所へ照会中。ReMHRADで把握できるのは入院期間を問わない在院患者数までで、1年以上の内訳と年齢区分は公表データにない</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>7</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>自立支援協議会の開催時期が未定</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>素案の合意時期が定まらず、パブリックコメント・印刷の日程も引けない</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>仕様書は開催1回程度を見込む。評価・素案・計画案の3段階を1回に集約する場合の構成を村と協議する</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>■ 直近のマイルストーン</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>時期</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>令和8年8月中</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定、調査票への設問追加の可否</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>村の回答。既に期限を超過している</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>令和8年8〜9月</t>
+          <t>令和8年8月中</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>アンケートの発送・回収</t>
+          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定、調査票への設問追加の可否</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -1049,63 +1034,63 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>上記3点の確定</t>
+          <t>村の回答。既に期限を超過している</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>令和8年9月</t>
+          <t>令和8年8〜9月</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>村実績データの受領（最優先6件）</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>アンケートの発送・回収</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>村の回答</t>
+          <t>上記3点の確定</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>令和8年10月</t>
+          <t>令和8年9月</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>集計 → 現行計画の評価の確定</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>村実績データの受領（最優先6件）</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>アンケートの回収</t>
+          <t>村の回答</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>令和8年11月</t>
+          <t>令和8年10月</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>見込量・成果目標・給付費の確定</t>
+          <t>集計 → 現行計画の評価の確定</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -1115,19 +1100,19 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>実績データの受領。算式は実装済み</t>
+          <t>アンケートの回収</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>令和8年12月</t>
+          <t>令和8年11月</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>素案の確定、自立支援協議会</t>
+          <t>見込量・成果目標・給付費の確定</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
@@ -1137,19 +1122,19 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>開催時期が未定</t>
+          <t>実績データの受領。算式は実装済み</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>令和9年1月</t>
+          <t>令和8年12月</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメント、調査結果報告書</t>
+          <t>素案の確定、自立支援協議会</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -1159,19 +1144,19 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>開催時期が未定</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>令和9年2月</t>
+          <t>令和9年1月</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>意見への対応、原稿確定、組版</t>
+          <t>パブリックコメント、調査結果報告書</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -1181,27 +1166,49 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>パブコメの終了</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>令和9年2月</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>意見への対応、原稿確定、組版</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>パブコメの終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>令和9年3月31日</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>納品（業務期間の末日）</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>全成果品の完成</t>
         </is>
@@ -1218,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2478,25 +2485,25 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J20" s="11" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>障がい者版52問・障がい児版51問。令和8年8月に村から朱書き修正指示40か所を受領し内容を確認済み（docs/北塩原村_アンケート調査票_村修正指示_確認結果.md）</t>
+          <t>令和8年8月25日版で確定（障がい者版45問・障がい児版44問）。村の朱書き修正指示40か所は反映済み。原典は source/アンケート/</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>修正の反映は調査票担当。問36（就労選択支援）の削除は当方から再考を依頼中。令和8年8月のマニュアルの標準項目との突合で、外出の目的・介護保険の利用状況・強度行動障害の該当有無の3件の欠落を確認。発送前の追加可否を村と協議する</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2755,27 +2762,27 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>P5 集計・分析</t>
+          <t>P4 ニーズ調査</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>データ入力</t>
+          <t>国のマニュアルとの差の代替設計</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>厚生労働省が提示する集計ファイル様式を基本として入力</t>
+          <t>確定版に無い国の標準項目4件について、確定版の設問の組み合わせと行政データとの突合で代替できるかを判定し、実施するクロス集計を設計</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(5)</t>
+          <t>仕様書4-Ⅰ(6)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2785,33 +2792,33 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>北塩原村_クロス集計設計.xlsx（7シート・クロス集計25件・行政データ突合6件）。介護保険・強度行動障害・障害支援区分の3件は行政データで代替可</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>アンケートの回収。集計様式の準備</t>
+          <t>外出の目的（第4次障がい者計画の指標）は代替できず、村との再協議が必要</t>
         </is>
       </c>
     </row>
@@ -2823,22 +2830,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>集計・分析の設計</t>
+          <t>データ入力</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>基本集計及び年齢・障がい種別等によるクロス集計。少数母数の取扱い</t>
+          <t>厚生労働省が提示する集計ファイル様式を基本として入力</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(6)</t>
+          <t>仕様書4-Ⅰ(5)</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -2848,7 +2855,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -2856,25 +2863,25 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J26" s="11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>3</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>アンケート集計分析方法（少数母数対応・計画接続メモ）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>小規模公表基準（n&lt;5の秘匿、地区別・障がい種別クロスの扱い）を村と合意する</t>
+          <t>アンケートの回収。集計様式の準備</t>
         </is>
       </c>
     </row>
@@ -2886,17 +2893,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>自由回答の取りまとめ</t>
+          <t>集計・分析の設計</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>自由記述の分類・要約。村の修正指示により問11-2・問37-2の自由記述欄が新設される</t>
+          <t>基本集計及び年齢・障がい種別等によるクロス集計。少数母数の取扱い</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2911,33 +2918,33 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>アンケート集計分析方法（少数母数対応・計画接続メモ）／北塩原村_クロス集計設計.xlsx（クロス集計25件・層6区分・行政データ突合6件）。想定有効回答は約110件のため層は3区分以下に束ねる設計とした</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>アンケートの回収</t>
+          <t>小規模公表基準（n&lt;5の秘匿、地区別・障がい種別クロスの扱い）を村と合意する</t>
         </is>
       </c>
     </row>
@@ -2949,22 +2956,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>成果目標との紐付け</t>
+          <t>自由回答の取りまとめ</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>現行計画は成果目標の設定根拠に調査結果報告書の頁番号を引用している。第8期でも同じ構造とするため、集計段階で設問と成果目標を紐付ける</t>
+          <t>自由記述の分類・要約。村の修正指示により問11-2・問37-2の自由記述欄が新設される</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)⑤</t>
+          <t>仕様書4-Ⅰ(6)</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -2995,12 +3002,12 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>現行計画評価 02_成果目標の評価に引用関係を整理済み</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>アンケートの集計</t>
+          <t>アンケートの回収</t>
         </is>
       </c>
     </row>
@@ -3012,22 +3019,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>調査結果報告書の作成</t>
+          <t>成果目標との紐付け</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>設問ごとにグラフを作成し、分析結果を報告書として取りまとめる</t>
+          <t>現行計画は成果目標の設定根拠に調査結果報告書の頁番号を引用している。第8期でも同じ構造とするため、集計段階で設問と成果目標を紐付ける</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅰ(7)・成果品②</t>
+          <t>仕様書4-Ⅱ(3)⑤</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -3037,12 +3044,12 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
           <t>2026-11</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>2026-12</t>
         </is>
       </c>
       <c r="I29" s="16" t="inlineStr">
@@ -3054,43 +3061,43 @@
         <v>0</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>現行計画評価 02_成果目標の評価に引用関係を整理済み</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>集計の完了</t>
+          <t>アンケートの集計</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>P6 現行計画の評価</t>
+          <t>P5 集計・分析</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>サービス利用実績の評価</t>
+          <t>調査結果報告書の作成</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>令和3〜5年度の見込量と実績を全数突合し、乖離の類型を判定</t>
+          <t>設問ごとにグラフを作成し、分析結果を報告書として取りまとめる</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(2)</t>
+          <t>仕様書4-Ⅰ(7)・成果品②</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -3100,33 +3107,33 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="J30" s="11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K30" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_現行計画評価.xlsx（7シート）。サービス25区分・地域生活支援事業16事業。計上漏れ・過大計上を特定</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>集計の完了</t>
         </is>
       </c>
     </row>
@@ -3138,17 +3145,17 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>成果目標の達成状況の評価</t>
+          <t>サービス利用実績の評価</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>第7期の成果目標7区分の現状値・目標値・設定根拠と評価の見通し</t>
+          <t>令和3〜5年度の見込量と実績を全数突合し、乖離の類型を判定</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3168,28 +3175,28 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K31" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>現行計画評価 02_成果目標の評価。令和8年8月の村の朱書きにより基幹相談支援センター未設置・セルフプラン率0％・医療的ケア児1人を確定</t>
+          <t>北塩原村_現行計画評価.xlsx（7シート）。サービス25区分・地域生活支援事業16事業。計上漏れ・過大計上を特定</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>令和6・7年度の実績と令和8年度見込（村へ依頼中）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3201,17 +3208,17 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>活動指標の達成状況の評価</t>
+          <t>成果目標の達成状況の評価</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>第7期の活動指標の実績。第8期は83項目のうち本村分65項目</t>
+          <t>第7期の成果目標7区分の現状値・目標値・設定根拠と評価の見通し</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3226,12 +3233,12 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
@@ -3240,19 +3247,19 @@
         </is>
       </c>
       <c r="J32" s="11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_活動指標.xlsx（4シート）で第8期の設定は完了</t>
+          <t>現行計画評価 02_成果目標の評価。令和8年8月の村の朱書きにより基幹相談支援センター未設置・セルフプラン率0％・医療的ケア児1人を確定</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の活動指標実績（村へ依頼中）</t>
+          <t>令和6・7年度の実績と令和8年度見込（村へ依頼中）</t>
         </is>
       </c>
     </row>
@@ -3264,22 +3271,22 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>第4次障がい者計画の施策目標値の測定</t>
+          <t>活動指標の達成状況の評価</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>8指標の測定手段を確認し、アンケートで測るもの・行政データで測るものを区分</t>
+          <t>第7期の活動指標の実績。第8期は83項目のうち本村分65項目</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(2)・4-Ⅱ(5)②</t>
+          <t>仕様書4-Ⅱ(2)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3289,60 +3296,60 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>現行計画評価 の施策指標8件。測定可能6・測定不能1・要確認1。外出目的の設問が調査票に無く1指標が測定できないことを特定</t>
+          <t>北塩原村_活動指標.xlsx（4シート）で第8期の設定は完了</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>令和6年度の活動指標実績（村へ依頼中）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>P7 推計・見込量</t>
+          <t>P6 現行計画の評価</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>推計方法の確定</t>
+          <t>第4次障がい者計画の施策目標値の測定</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>個別積上げ方式（実績・意向・心身の状況を利用者単位で積み上げる方法）。別表第五の適用判定を含む</t>
+          <t>8指標の測定手段を確認し、アンケートで測るもの・行政データで測るものを区分</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)</t>
+          <t>仕様書4-Ⅱ(2)・4-Ⅱ(5)②</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -3369,11 +3376,11 @@
         <v>100</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_サービス見込量.xlsx（13シート）。11_告示別表第一根拠・12_別表第五判定。全域過疎により別表第五は適用対象外と確定し、個別積上げ方式を採用</t>
+          <t>現行計画評価 の施策指標8件。測定可能6・測定不能1・要確認1。外出目的の設問が調査票に無く1指標が測定できないことを特定</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
@@ -3390,22 +3397,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>障がい福祉サービスの見込量の推計</t>
+          <t>推計方法の確定</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>介護給付・訓練等給付の利用者数と量。年齢到達に伴う移行を含む</t>
+          <t>個別積上げ方式（実績・意向・心身の状況を利用者単位で積み上げる方法）。別表第五の適用判定を含む</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)②</t>
+          <t>仕様書4-Ⅱ(3)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3420,28 +3427,28 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="K35" s="11" t="n">
         <v>5</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>算式は実装済み（02〜04）。障害支援区分別人数15人による検証を実施し、既存の見込量と矛盾しないことを確認</t>
+          <t>北塩原村_サービス見込量.xlsx（13シート）。11_告示別表第一根拠・12_別表第五判定。全域過疎により別表第五は適用対象外と確定し、個別積上げ方式を採用</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>年齢別・サービス別の匿名利用者一覧、サービス別の支給決定者数（村へ依頼中）</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3453,22 +3460,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>障がい児通所支援等の見込量の推計</t>
+          <t>障がい福祉サービスの見込量の推計</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>児童発達支援・放課後等デイサービス等の利用者数と量</t>
+          <t>介護給付・訓練等給付の利用者数と量。年齢到達に伴う移行を含む</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)③</t>
+          <t>仕様書4-Ⅱ(3)②</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -3492,19 +3499,19 @@
         </is>
       </c>
       <c r="J36" s="11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>算式は実装済み（04）。障がい児入所0件・通所支援の申請中0件を村の朱書きで確認</t>
+          <t>算式は実装済み（02〜04）。障害支援区分別人数15人による検証を実施し、既存の見込量と矛盾しないことを確認</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>令和6・7年度の障害児給付費の変動理由（児童発達支援23件→1件、放課後等デイ12件→27件）の確認</t>
+          <t>年齢別・サービス別の匿名利用者一覧、サービス別の支給決定者数（村へ依頼中）</t>
         </is>
       </c>
     </row>
@@ -3516,22 +3523,22 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>地域生活支援事業の見込量の推計</t>
+          <t>障がい児通所支援等の見込量の推計</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>必須15事業・任意3事業の事業ごとの実施に関する考え方と量の見込み</t>
+          <t>児童発達支援・放課後等デイサービス等の利用者数と量</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)④</t>
+          <t>仕様書4-Ⅱ(3)③</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3546,28 +3553,28 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_地域生活支援事業.xlsx（4シート）。告示第三の二の3の4事項に対応</t>
+          <t>算式は実装済み（04）。障がい児入所0件・通所支援の申請中0件を村の朱書きで確認</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>移動支援0人・福祉ホームの実績と見込の逆転など、確認事項7件が未解消</t>
+          <t>令和6・7年度の障害児給付費の変動理由（児童発達支援23件→1件、放課後等デイ12件→27件）の確認</t>
         </is>
       </c>
     </row>
@@ -3579,22 +3586,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>地域生活支援事業の見込量の推計</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>第8期の成果目標8区分（人材確保・定着が新設）</t>
+          <t>必須15事業・任意3事業の事業ごとの実施に関する考え方と量の見込み</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)⑤</t>
+          <t>仕様書4-Ⅱ(3)④</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -3609,28 +3616,28 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J38" s="11" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版 第4章。国基準数値を告示本文と照合済み。村の朱書きにより（３）（４）（６）を具体化</t>
+          <t>北塩原村_地域生活支援事業.xlsx（4シート）。告示第三の二の3の4事項に対応</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>令和7年度末の施設入所者数、令和6年度の一般就労移行実績、1年以上長期入院者の実数</t>
+          <t>移動支援0人・福祉ホームの実績と見込の逆転など、確認事項7件が未解消</t>
         </is>
       </c>
     </row>
@@ -3642,17 +3649,17 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>7-6</t>
+          <t>7-5</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>活動指標の設定</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>別表第一の83項目から本村で設定する65項目を選定。告示第三の四㈡により見込量以外の活動指標は任意</t>
+          <t>第8期の成果目標8区分（人材確保・定着が新設）</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3672,28 +3679,28 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_活動指標.xlsx。設定51・検討7・設定しない7・都道府県指標18</t>
+          <t>骨子案修正版 第4章。国基準数値を告示本文と照合済み。村の朱書きにより（３）（４）（６）を具体化</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>令和6年度実績の受領後に現状値を入れる</t>
+          <t>令和7年度末の施設入所者数、令和6年度の一般就労移行実績、1年以上長期入院者の実数</t>
         </is>
       </c>
     </row>
@@ -3705,22 +3712,22 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>7-6</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>給付費・財源構成の推計</t>
+          <t>活動指標の設定</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>サービス別の給付費と、国1/2・県1/4・村1/4の法定負担による財源構成</t>
+          <t>別表第一の83項目から本村で設定する65項目を選定。告示第三の四㈡により見込量以外の活動指標は任意</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(3)</t>
+          <t>仕様書4-Ⅱ(3)⑤</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
@@ -3735,55 +3742,55 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J40" s="11" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>北塩原村_財源構成案.xlsx。年間給付費＝利用者数×単価×12×改定率で算式化。令和8・9年度の報酬改定率をパラメータ化済み</t>
+          <t>北塩原村_活動指標.xlsx。設定51・検討7・設定しない7・都道府県指標18</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>見込量の確定、障がい福祉関係の歳入歳出決算（村へ依頼中）</t>
+          <t>令和6年度実績の受領後に現状値を入れる</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>P8 施策検討・計画案</t>
+          <t>P7 推計・見込量</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>障がい者福祉施策の検討</t>
+          <t>給付費・財源構成の推計</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>現行計画の成果と課題を踏まえ、次期計画に盛り込む施策を検討</t>
+          <t>サービス別の給付費と、国1/2・県1/4・村1/4の法定負担による財源構成</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(4)</t>
+          <t>仕様書4-Ⅱ(3)</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3801,25 +3808,25 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K41" s="11" t="n">
         <v>4</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版 第3章（基本理念・基本目標及び施策体系）。第8期で加わる視点と施策体系の対応表を新設</t>
+          <t>北塩原村_財源構成案.xlsx。年間給付費＝利用者数×単価×12×改定率で算式化。令和8・9年度の報酬改定率をパラメータ化済み</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>現行計画の評価の確定</t>
+          <t>見込量の確定、障がい福祉関係の歳入歳出決算（村へ依頼中）</t>
         </is>
       </c>
     </row>
@@ -3831,22 +3838,22 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>障がい者福祉施策の検討</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>仕様書が定める記載事項8項目（基本理念・施策体系・手帳所持者数の将来推計・サービス見込量・障がい児通所支援等の見込量・地域生活支援事業の見込量・成果目標及び活動指標・推進体制及び進行管理）</t>
+          <t>現行計画の成果と課題を踏まえ、次期計画に盛り込む施策を検討</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(5)</t>
+          <t>仕様書4-Ⅱ(4)</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr">
@@ -3856,12 +3863,12 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
@@ -3870,19 +3877,19 @@
         </is>
       </c>
       <c r="J42" s="11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版（全8章・97表・369段落・図9点）。推計方法・年齢到達移行・活動指標・財源構成の4節を新設</t>
+          <t>骨子案修正版 第3章（基本理念・基本目標及び施策体系）。第8期で加わる視点と施策体系の対応表を新設</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>アンケート結果、実績データ、見込量の確定</t>
+          <t>現行計画の評価の確定</t>
         </is>
       </c>
     </row>
@@ -3894,17 +3901,17 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>確保のための方策の記載</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小規模町村・中山間地域向けの確保方策。介護保険事業所への指定働きかけ、共生型サービス、基準該当、多機能型・従たる事業所、短期入所</t>
+          <t>仕様書が定める記載事項8項目（基本理念・施策体系・手帳所持者数の将来推計・サービス見込量・障がい児通所支援等の見込量・地域生活支援事業の見込量・成果目標及び活動指標・推進体制及び進行管理）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -3919,33 +3926,33 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>骨子案修正版 第5章8。告示が名指しする5つの具体策を反映し、圏域の事業所数を原典から表として生成する方式に変更</t>
+          <t>骨子案修正版（全8章・97表・369段落・図9点）。推計方法・年齢到達移行・活動指標・財源構成の4節を新設</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>アンケート結果、実績データ、見込量の確定</t>
         </is>
       </c>
     </row>
@@ -3957,22 +3964,22 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>分量配分の設計</t>
+          <t>確保のための方策の記載</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>成果品①は約60頁。章別の目標頁数を先に決め、原稿段階で収める</t>
+          <t>小規模町村・中山間地域向けの確保方策。介護保険事業所への指定働きかけ、共生型サービス、基準該当、多機能型・従たる事業所、短期入所</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品①</t>
+          <t>仕様書4-Ⅱ(5)</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -3999,11 +4006,11 @@
         <v>100</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>計画書_分量配分計画（docs）。現行63頁の章別配分を基準に60頁へ配分。削減順序と削ってはならないものを明記</t>
+          <t>骨子案修正版 第5章8。告示が名指しする5つの具体策を反映し、圏域の事業所数を原典から表として生成する方式に変更</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -4015,27 +4022,27 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P8 施策検討・計画案</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>自立支援協議会の資料作成</t>
+          <t>分量配分の設計</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>委託者が協議会に報告・説明し、受託者は会議資料の作成、会議への出席、会議記録（要旨）の作成等の運営支援を行う。開催は1回程度</t>
+          <t>成果品①は約60頁。章別の目標頁数を先に決め、原稿段階で収める</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(7)</t>
+          <t>仕様書5 成果品①</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -4050,28 +4057,28 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>会議資料5点を作成（協議会資料1・2・8、庁議資料2・4）。村資料に依存しない資料を先行して整備</t>
+          <t>計画書_分量配分計画（docs）。現行63頁の章別配分を基準に60頁へ配分。削減順序と削ってはならないものを明記</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>協議会の開催時期が未定。委員名簿が未受領</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4083,17 +4090,17 @@
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>協議会の開催</t>
+          <t>自立支援協議会の資料作成</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>調査結果・素案・計画案の報告と審議</t>
+          <t>委託者が協議会に報告・説明し、受託者は会議資料の作成、会議への出席、会議記録（要旨）の作成等の運営支援を行う。開催は1回程度</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -4103,38 +4110,38 @@
       </c>
       <c r="F46" s="11" t="inlineStr">
         <is>
-          <t>北塩原村・受託者</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>会議資料5点を作成（協議会資料1・2・8、庁議資料2・4）。村資料に依存しない資料を先行して整備</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>開催日が未定。素案の確定</t>
+          <t>協議会の開催時期が未定。委員名簿が未受領</t>
         </is>
       </c>
     </row>
@@ -4146,22 +4153,22 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>庁議の開催</t>
+          <t>協議会の開催</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>庁内各課との調整。関連計画との整合と依頼事項</t>
+          <t>調査結果・素案・計画案の報告と審議</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>仕様書4-Ⅱ(7)</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4171,12 +4178,12 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
@@ -4188,16 +4195,16 @@
         <v>0</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>庁議資料2点は作成済み</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>開催時期が未定</t>
+          <t>開催日が未定。素案の確定</t>
         </is>
       </c>
     </row>
@@ -4209,22 +4216,22 @@
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>庁議の開催</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>計画案について意見を募集し、得られた意見を反映</t>
+          <t>庁内各課との調整。関連計画との整合と依頼事項</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>仕様書4-Ⅱ(6)</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -4234,12 +4241,12 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
           <t>2027-01</t>
-        </is>
-      </c>
-      <c r="H48" s="11" t="inlineStr">
-        <is>
-          <t>2027-02</t>
         </is>
       </c>
       <c r="I48" s="16" t="inlineStr">
@@ -4251,16 +4258,16 @@
         <v>0</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>庁議資料2点は作成済み</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>素案の確定。実施時期が未定</t>
+          <t>開催時期が未定</t>
         </is>
       </c>
     </row>
@@ -4272,17 +4279,17 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>意見の整理、対応案の作成、計画への反映</t>
+          <t>計画案について意見を募集し、得られた意見を反映</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -4292,12 +4299,12 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>北塩原村・受託者</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -4323,29 +4330,29 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>素案の確定。実施時期が未定</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>計画書の原稿確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>協議会・パブリックコメントを経て得られた意見を反映の上、最終的に取りまとめる</t>
+          <t>意見の整理、対応案の作成、計画への反映</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4377,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
@@ -4386,7 +4393,7 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
     </row>
@@ -4398,22 +4405,22 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>10-2</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>レイアウト・組版</t>
+          <t>計画書の原稿確定</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>A4判・両面・約60頁・モノクロ</t>
+          <t>協議会・パブリックコメントを経て得られた意見を反映の上、最終的に取りまとめる</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品①</t>
+          <t>仕様書4-Ⅱ(6)</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4428,7 +4435,7 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="I51" s="16" t="inlineStr">
@@ -4444,12 +4451,12 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>分量配分計画を作成済み。実際の組版で1頁あたりの文字数を実測し補正する</t>
+          <t>―</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>原稿の確定</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4461,17 +4468,17 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-2</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>校正</t>
+          <t>レイアウト・組版</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>村の確認を経て校了</t>
+          <t>A4判・両面・約60頁・モノクロ</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4481,12 +4488,12 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>受託者・北塩原村</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -4503,16 +4510,16 @@
         <v>0</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>分量配分計画を作成済み。実際の組版で1頁あたりの文字数を実測し補正する</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>原稿の確定</t>
         </is>
       </c>
     </row>
@@ -4524,27 +4531,27 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>校正</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>計画書はコピー・くるみ製本30部、調査報告書はコピー・ホチキス製本10部</t>
+          <t>村の確認を経て校了</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品①②</t>
+          <t>仕様書5 成果品①</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・北塩原村</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4575,7 +4582,7 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>校了。印刷業者の手配</t>
+          <t>組版</t>
         </is>
       </c>
     </row>
@@ -4587,22 +4594,22 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>電子媒体の作成</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>計画書と調査報告書の電子データ一式</t>
+          <t>計画書はコピー・くるみ製本30部、調査報告書はコピー・ホチキス製本10部</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>仕様書5 成果品③</t>
+          <t>仕様書5 成果品①②</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -4629,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
@@ -4638,7 +4645,7 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>編集可能形式とPDFの別を村に確認する</t>
+          <t>校了。印刷業者の手配</t>
         </is>
       </c>
     </row>
@@ -4650,27 +4657,27 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>電子媒体の作成</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>令和9年3月31日まで</t>
+          <t>計画書と調査報告書の電子データ一式</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>仕様書3（業務期間）</t>
+          <t>仕様書5 成果品③</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>受託者・北塩原村</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4701,12 +4708,75 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
+          <t>編集可能形式とPDFの別を村に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>P10 完成・納品</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>納品・検収</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>令和9年3月31日まで</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>仕様書3（業務期間）</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>受託者・北塩原村</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H56" s="11" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
           <t>全成果品の完成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:M56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4797,31 +4867,31 @@
         </is>
       </c>
       <c r="B2" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A2)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A2,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A2,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A2,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A2,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A2,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A2,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A2)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A2)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A2)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A2)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A2)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A2)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I2" s="11" t="inlineStr">
@@ -4847,31 +4917,31 @@
         </is>
       </c>
       <c r="B3" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A3)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A3,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A3,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A3,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A3,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A3,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A3,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A3)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A3)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A3)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A3)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A3)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A3)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -4897,31 +4967,31 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A4)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A4,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A4,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A4,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A4,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A4,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A4,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A4)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A4)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A4)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A4)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A4)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A4)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -4947,31 +5017,31 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A5)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A5,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A5,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A5,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A5,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A5,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A5,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A5)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A5)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A5)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A5)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A5)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A5)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -4997,31 +5067,31 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A6)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A6,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A6,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A6,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A6,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A6,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A6,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A6)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A6)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A6)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A6)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A6)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A6)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -5047,31 +5117,31 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A7)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A7,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A7,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A7,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A7,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A7,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A7,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A7)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A7)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A7)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A7)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A7)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A7)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -5097,31 +5167,31 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A8)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A8,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A8,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A8,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A8,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A8,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A8,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A8)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A8)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A8)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A8)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A8)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A8)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -5147,31 +5217,31 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A9)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A9,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A9,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A9,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A9,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A9,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A9,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A9)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A9)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A9)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A9)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A9)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A9)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -5197,31 +5267,31 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A10)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A10,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A10,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A10,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A10,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A10,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A10,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H10" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A10)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A10)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A10)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A10)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A10)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A10)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -5247,31 +5317,31 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>COUNTIF('01_WBS'!$A$2:$A$55,$A11)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$56,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A11,'01_WBS'!$I$2:$I$56,"完了")</f>
         <v/>
       </c>
       <c r="D11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A11,'01_WBS'!$I$2:$I$56,"進行中")</f>
         <v/>
       </c>
       <c r="E11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A11,'01_WBS'!$I$2:$I$56,"要対応")</f>
         <v/>
       </c>
       <c r="F11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A11,'01_WBS'!$I$2:$I$56,"データ待ち")</f>
         <v/>
       </c>
       <c r="G11" s="11">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$55,$A11,'01_WBS'!$I$2:$I$55,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$56,$A11,'01_WBS'!$I$2:$I$56,"未着手")</f>
         <v/>
       </c>
       <c r="H11" s="17">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A11)*'01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A11)*'01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT(('01_WBS'!$A$2:$A$55=$A11)*'01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A11)*'01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A11)*'01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT(('01_WBS'!$A$2:$A$56=$A11)*'01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -5321,7 +5391,7 @@
         <v/>
       </c>
       <c r="H12" s="19">
-        <f>IF(SUMPRODUCT('01_WBS'!$K$2:$K$55)=0,0,SUMPRODUCT('01_WBS'!$J$2:$J$55*'01_WBS'!$K$2:$K$55)/SUMPRODUCT('01_WBS'!$K$2:$K$55)/100)</f>
+        <f>IF(SUMPRODUCT('01_WBS'!$K$2:$K$56)=0,0,SUMPRODUCT('01_WBS'!$J$2:$J$56*'01_WBS'!$K$2:$K$56)/SUMPRODUCT('01_WBS'!$K$2:$K$56)/100)</f>
         <v/>
       </c>
       <c r="I12" s="18" t="inlineStr">
@@ -5599,7 +5669,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定、調査票への設問追加の可否（外出の目的・介護保険・強度行動障害）</t>
+          <t>印刷仕様の確定、宛名ラベルの受領、対象者数の確定</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -5614,7 +5684,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>アンケート発送のクリティカルパス。いずれも未了。設問追加は令和8年8月の国のマニュアルの標準項目に関するもので、発送前でなければ対応できない</t>
+          <t>アンケート発送のクリティカルパス。いずれも未了。調査票は8月25日版で確定済み</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6619,12 +6689,12 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最優先</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>PDCAの評価体制・スケジュール・公表方法</t>
+          <t>要介護認定の有無・要介護度（匿名利用者一覧への列追加）</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -6640,19 +6710,19 @@
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>自立支援協議会と庁内会議体の役割分担、実績把握と評価の時期（村の予算編成に合わせる）、中間評価の結果の公表方法（ホームページ・広報誌・協議会資料の公開範囲）／反映先：骨子案修正版 第1章6／希望期限：2026-12-31</t>
+          <t>依頼済みの「年齢別・サービス別の匿名利用者一覧」に、要介護認定の有無・要介護度・利用している介護保険サービスの列を追加。確定版の調査票に介護保険の設問がないため、これが唯一の把握手段になる／反映先：クロス集計設計 A-1／サービス見込量 06_65歳移行判定／希望期限：2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>高</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>アンケート調査票への村の修正指示</t>
+          <t>PDCAの評価体制・スケジュール・公表方法</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -6660,27 +6730,27 @@
           <t>北塩原村</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>完了</t>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている／反映先：村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果／希望期限：2026-08-14</t>
+          <t>自立支援協議会と庁内会議体の役割分担、実績把握と評価の時期（村の予算編成に合わせる）、中間評価の結果の公表方法（ホームページ・広報誌・協議会資料の公開範囲）／反映先：骨子案修正版 第1章6／希望期限：2026-12-31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>―</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
+          <t>アンケート調査票への村の修正指示</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -6688,15 +6758,15 @@
           <t>北塩原村</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>関連計画との整合確認／反映先：計画本文 第1章・第7章／希望期限：2026-10-31</t>
+          <t>【受領済み】障がい者版17頁・障がい児版19頁のスキャンPDF。朱書き40か所。設問の削除・追加・順序変更のほか、削除理由として村の実データ9件が書き添えられている／反映先：村提供実績データ 05／北塩原村_アンケート調査票_村修正指示_確認結果／希望期限：2026-08-14</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6778,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>40歳以上65歳未満の特定疾病該当者</t>
+          <t>第5次総合振興計画たたき台、健康21現行計画、高齢者福祉・介護保険事業計画</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -6724,7 +6794,7 @@
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>16の特定疾病に該当し要介護認定を受けている方の有無／反映先：サービス見込量 02／希望期限：2026-10-31</t>
+          <t>関連計画との整合確認／反映先：計画本文 第1章・第7章／希望期限：2026-10-31</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6806,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>自立支援協議会の委員名簿</t>
+          <t>40歳以上65歳未満の特定疾病該当者</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -6752,12 +6822,40 @@
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="5" t="inlineStr">
         <is>
+          <t>16の特定疾病に該当し要介護認定を受けている方の有無／反映先：サービス見込量 02／希望期限：2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>自立支援協議会の委員名簿</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>北塩原村</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>任期・氏名・所属・役職／反映先：計画書 資料編／希望期限：2026-12-31</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>※ No 列は優先度。依頼の詳細は 北塩原村_業務進捗管理.xlsx 04_村資料受領状況 を参照。</t>
         </is>
@@ -6956,7 +7054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7438,12 +7536,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>発送前であれば既存設問への選択肢追加で対応する。追加しない場合は支給決定者台帳と介護保険の認定情報の突合に一本化する</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>調査票が令和8年8月25日版で確定したため設問の追加は不可。支給決定者台帳と介護保険の要介護認定情報の突合に一本化する（クロス集計設計 A-1）。依頼済みの匿名利用者一覧に要介護認定の列を1つ追加する。アンケート側は問2×問27-1（C-12）、問2×問7（C-13）、問2×問27-3（C-14）で補う</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7568,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>発送前であれば問13の後に外出目的の設問を追加するか、問45の選択肢を前回に揃える。発送後であれば別の把握方法へ切り替える旨を村と協議する</t>
+          <t>調査票が確定したため設問の追加は不可。確定版で最も近い問42は「今後参加したいもの」という意向であり、実態を問う前回値28.1%と接続できない。第4次障がい者計画は改定対象外のため、指標の測定方法の変更は村の判断事項。村との再協議が必要（クロス集計設計 S-1）</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -7598,12 +7696,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>発送前であれば設問を追加する。追加しない場合は、村の朱書きで判明した区分6の2人について行動関連項目の点数を確認する（既に照会中）</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>調査票が確定したため設問の追加は不可。問19で「特にない」以外を選んだ回答をニーズ層として扱い（C-15・C-16）、実数は行政データ（区分6の2人の行動関連項目、行動援護の支給決定者数）で押さえる（クロス集計設計 A-2）。アンケートでは母数を特定できない旨を計画に明記する</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
     </row>
@@ -7630,42 +7728,74 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>国の標準項目である旨を村へ伝えたうえで最終判断をいただく。当方の見解は変わらず、削除でも支障はない（区分別人数は役場データで把握済み）</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>令和8年8月25日版で削除が確定した。区分別人数15人は村から受領済みで、見込量の推計に支障はない。アンケート側は「重度層（代理指標）」で層別する（クロス集計設計 03・C-17）。区分別クロス集計ができないことは計画に明記する</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>R-22</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>国のマニュアルの発出と調査票の確定の時期が重なった</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>マニュアルは令和8年8月19日事務連絡（県通知8月24日）、調査票の確定は8月25日版。標準項目3件の欠落は、当方の設計の不備ではなくこの時期の重なりによる。第9期の策定時に同じ論点が生じうる</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>調査設計／影響度中</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>経緯を打合せ記録に残し、計画書の調査概要にも「調査票確定後に国のマニュアルが改定された」旨を注記する（クロス集計設計 S-4）。算定根拠への疑義に対する説明にもなる</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>R-19</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>障がい児版の設問番号に誤りがある</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>問11の選択肢番号「13」が2つある（「自傷、他害、強いこだわり、パニックなどへの対応」と「特にない」）。問10の選択肢番号は「3」が欠番。いずれも村の朱書きとは別に、通読して気づいたもの</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>調査設計／影響度低</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>調査票担当へ申し送り済み。印刷前に番号を振り直す。問10は問8との統合指示があるため、統合時に整理する</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
@@ -7682,7 +7812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7907,21 +8037,21 @@
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>国のマニュアルの改定</t>
+          <t>調査票の確定と国の標準項目の欠落</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月に「障害福祉計画策定に係る実態調査及びPDCAサイクルに関するマニュアル」が改定され、福島県から市町村へ通知された。調査票の標準項目と、見込量推計・PDCAサイクルの要求水準が示された</t>
+          <t>調査票は令和8年8月25日版で確定し設問の追加ができない。国のマニュアルの標準項目のうち、外出の目的・介護保険の利用状況・強度行動障害の該当有無・障害支援区分の4件が確定版にない</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>厚労省・こども家庭庁 令和8年8月19日事務連絡／福島県 8生福第2646号・8こ第2041号 令和8年8月24日</t>
+          <t>仕様書4-Ⅰ(2)（委託者との協議の上決定）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -7931,42 +8061,72 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>確認結果を文書化済み。別表第五の適用外判定は裏付けられた。調査票の欠落3件について発送前に村と協議する必要がある</t>
+          <t>クロス集計設計.xlsx で代替方針を整理済み。3件は行政データで代替可。外出の目的のみ村との再協議が必要</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>国のマニュアルの改定</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月に「障害福祉計画策定に係る実態調査及びPDCAサイクルに関するマニュアル」が改定され、福島県から市町村へ通知された。調査票の標準項目と、見込量推計・PDCAサイクルの要求水準が示された</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>厚労省・こども家庭庁 令和8年8月19日事務連絡／福島県 8生福第2646号・8こ第2041号 令和8年8月24日</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>確認結果を文書化済み。別表第五の適用外判定は裏付けられた。調査票の欠落3件について発送前に村と協議する必要がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>調査票の修正指示</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>令和8年8月に村から朱書き40か所の修正指示を受領。うち9件は削除理由として村の実データが書き添えられていた</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>仕様書4-Ⅰ(2)（委託者との協議の上決定）</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>確認結果を文書化済み（docs/北塩原村_アンケート調査票_村修正指示_確認結果.md）。問36の削除について再考を依頼中</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>※ 仕様書6(3)により北塩原村委託契約約款に準拠する。仕様書と異なる運用は書面で記録を残す。</t>
         </is>
